--- a/132_Cuenca_Quilca_-_Vitor_-_Chili/_raw_reportes_xlsx/IDConfig_64993_completo.xlsx
+++ b/132_Cuenca_Quilca_-_Vitor_-_Chili/_raw_reportes_xlsx/IDConfig_64993_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rfd1094a2659947f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R8a4313871a4349a8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2089</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2346</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1731</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2404</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2744</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2559</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1592</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1658</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1615</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>
@@ -429,7 +564,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.8282</x:v>
+        <x:v>      0.1879</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -444,7 +579,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.9537</x:v>
+        <x:v>      0.1751</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -459,7 +594,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.3541</x:v>
+        <x:v>      0.1530</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -474,7 +609,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.6552</x:v>
+        <x:v>      0.1680</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -489,7 +624,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.6464</x:v>
+        <x:v>      0.1718</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -504,7 +639,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.4982</x:v>
+        <x:v>      0.1660</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -519,7 +654,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.5470</x:v>
+        <x:v>      0.1746</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -534,7 +669,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.9750</x:v>
+        <x:v>      0.1846</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -549,7 +684,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.8142</x:v>
+        <x:v>      0.1672</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -564,7 +699,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.0415</x:v>
+        <x:v>      0.1606</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -579,7 +714,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.1974</x:v>
+        <x:v>      0.1409</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -594,7 +729,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2001</x:v>
+        <x:v>      0.1616</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -609,7 +744,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.3537</x:v>
+        <x:v>      0.1690</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -624,7 +759,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2305</x:v>
+        <x:v>      0.1745</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -639,7 +774,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.6729</x:v>
+        <x:v>      0.1509</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -654,7 +789,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.7997</x:v>
+        <x:v>      0.1710</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -669,7 +804,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.7397</x:v>
+        <x:v>      0.2150</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -684,7 +819,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.4102</x:v>
+        <x:v>      0.1787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -699,7 +834,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.1183</x:v>
+        <x:v>      0.1851</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -714,7 +849,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.8746</x:v>
+        <x:v>      0.2094</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -729,7 +864,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.8258</x:v>
+        <x:v>      0.1834</x:v>
       </x:c>
     </x:row>
     <x:row>

--- a/132_Cuenca_Quilca_-_Vitor_-_Chili/_raw_reportes_xlsx/IDConfig_64993_completo.xlsx
+++ b/132_Cuenca_Quilca_-_Vitor_-_Chili/_raw_reportes_xlsx/IDConfig_64993_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R8a4313871a4349a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Re5b09b1fda9b4b18"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1314</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1453</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1634</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1433</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1473</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1586</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1555</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1631</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1555</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1433</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1378</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1631</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1771</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1726</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1667</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1565</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1628</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1427</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1495</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1733</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1489</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1754</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1647</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1576</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1874</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1537</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2004</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1530</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1665</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2101</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1913</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2015</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2161</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1934</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2089</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1823</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1765</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1828</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2256</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2270</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1873</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2105</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1654</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1583</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1788</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2337</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1873</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +984,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2089</x:v>
+        <x:v>      0.1841</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -279,7 +999,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2346</x:v>
+        <x:v>      0.2311</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -294,7 +1014,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1731</x:v>
+        <x:v>      0.1720</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -309,7 +1029,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2404</x:v>
+        <x:v>      0.2377</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -324,7 +1044,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2744</x:v>
+        <x:v>      0.2719</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -339,7 +1059,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2559</x:v>
+        <x:v>      0.2519</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -354,7 +1074,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1592</x:v>
+        <x:v>      0.1585</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -369,7 +1089,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1658</x:v>
+        <x:v>      0.1653</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -384,7 +1104,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1615</x:v>
+        <x:v>      0.1606</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -399,7 +1119,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1463</x:v>
+        <x:v>      0.1462</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -414,7 +1134,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1578</x:v>
+        <x:v>      0.1577</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -429,7 +1149,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1626</x:v>
+        <x:v>      0.1622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -444,7 +1164,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2142</x:v>
+        <x:v>      0.2126</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -459,7 +1179,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1925</x:v>
+        <x:v>      0.1895</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -474,7 +1194,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1796</x:v>
+        <x:v>      0.1781</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -489,7 +1209,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2317</x:v>
+        <x:v>      0.2308</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -504,7 +1224,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2810</x:v>
+        <x:v>      0.2794</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -519,7 +1239,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1996</x:v>
+        <x:v>      0.1974</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -534,7 +1254,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1792</x:v>
+        <x:v>      0.1777</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -549,7 +1269,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1987</x:v>
+        <x:v>      0.1978</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -564,7 +1284,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1879</x:v>
+        <x:v>      0.2252</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -579,7 +1299,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1751</x:v>
+        <x:v>      0.1993</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -594,7 +1314,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1530</x:v>
+        <x:v>      0.1534</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -609,7 +1329,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1680</x:v>
+        <x:v>      0.1806</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -624,7 +1344,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1718</x:v>
+        <x:v>      0.2065</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -639,7 +1359,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1660</x:v>
+        <x:v>      0.1917</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -654,7 +1374,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1746</x:v>
+        <x:v>      0.2109</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -669,28 +1389,913 @@
         </x:is>
       </x:c>
       <x:c s="3">
+        <x:v>      0.2221</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1730</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1837</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1494</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1962</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1917</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2109</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1610</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1917</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2457</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1917</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2189</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2252</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2149</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2717</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2181</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1650</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
         <x:v>      0.1846</x:v>
       </x:c>
     </x:row>
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>26/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1672</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>25/07/2026</x:t>
+          <x:t>09/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2194</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1810</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1614</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2390</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2569</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2717</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2453</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2337</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2453</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2497</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2189</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2613</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1949</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1801</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1502</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2065</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1730</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2105</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1542</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2185</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1462</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2382</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2417</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1725</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1650</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1766</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2302</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1842</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1761</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1422</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1462</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1422</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1877</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2261</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2034</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1690</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1382</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1422</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1726</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1842</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1802</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1262</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1302</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/05/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -705,367 +2310,1132 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>24/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1409</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>23/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1616</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>22/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1690</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>21/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1745</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>20/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1509</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>19/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1710</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>18/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2150</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>17/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1787</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>16/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1851</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>15/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2094</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>14/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1834</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>13/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.3011</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>12/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2325</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>11/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1844</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>10/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1784</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>09/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2553</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>08/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1887</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>07/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2253</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>06/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2793</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>05/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2477</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>04/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2953</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>03/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2776</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>02/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2544</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>01/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2431</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>30/06/2026</x:t>
+          <x:t>26/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1382</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1342</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1422</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1904</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1422</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1182</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1262</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1142</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1382</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1570</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1454</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1582</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1382</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1382</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1374</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1622</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1422</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1382</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1422</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1222</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1462</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1462</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1262</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1142</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1342</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1342</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1302</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1570</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1917</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1342</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1570</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1222</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1382</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1342</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1993</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1494</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1494</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1382</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1302</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1645</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1810</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1502</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1342</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1922</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2685</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2601</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3761</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2373</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3413</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4573</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3033</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3645</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3297</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2917</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5665</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5153</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7089</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3335</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2246</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2066</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1938</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1593</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1354</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1569</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1373</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1569</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1569</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1599</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1859</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2269</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1984</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2242</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2044</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/03/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -1080,1656 +3450,6 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>29/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2439</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>28/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2618</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>27/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2061</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>26/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1903</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>25/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1904</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>24/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2246</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>23/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2225</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>22/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2387</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>21/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2043</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>20/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2124</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>19/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2115</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>18/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2407</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>17/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2273</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>16/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1838</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>15/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1644</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>14/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2177</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>13/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2202</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>12/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1843</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>11/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1888</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>10/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1470</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>09/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1517</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>08/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1693</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>07/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2224</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>06/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2249</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>05/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1789</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>04/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1627</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>03/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1471</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>02/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1543</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>01/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2028</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>31/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1648</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>30/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1613</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>29/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1439</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>28/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1465</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>27/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1534</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>26/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1411</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>25/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1436</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>24/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1539</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>23/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1749</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>22/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1589</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>21/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1673</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>20/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1673</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>19/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1377</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>18/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1439</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>17/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1729</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>16/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1455</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>15/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1542</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>14/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1542</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>13/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1463</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>12/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1791</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>11/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1697</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>10/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1482</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>09/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1504</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>08/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1498</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>07/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1665</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>06/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1743</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>05/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1432</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>04/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1459</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>03/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1390</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>02/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1383</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>01/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1504</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>30/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1458</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>29/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1564</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>28/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1831</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>27/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1547</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>26/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1641</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>25/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1391</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>24/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1406</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>23/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1925</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>22/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1858</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>21/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1774</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>20/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1709</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>19/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1504</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>18/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1454</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>17/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1615</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>16/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1812</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>15/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1577</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>14/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1428</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>13/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1908</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>12/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2676</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>11/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2743</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>10/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.3752</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>09/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2951</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>08/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.3447</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>07/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.4360</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>06/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.3096</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>05/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.3733</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>04/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.3114</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>03/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.3021</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>02/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.5371</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>01/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.4971</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>31/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.7063</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>30/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.3344</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>29/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2282</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>28/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2111</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>27/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1785</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>26/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1950</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>25/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1615</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>24/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1418</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>23/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1626</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>22/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1695</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>21/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1366</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>20/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1576</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>19/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1568</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>18/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1597</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>17/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1868</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>16/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2301</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>15/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2030</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>14/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2294</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>13/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2061</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>12/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2434</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
           <x:t>11/03/2026</x:t>
         </x:is>
       </x:c>
@@ -2739,7 +3459,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2440</x:v>
+        <x:v>      0.2388</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2754,7 +3474,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3916</x:v>
+        <x:v>      0.3935</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2769,7 +3489,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4635</x:v>
+        <x:v>      0.4689</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2784,7 +3504,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4416</x:v>
+        <x:v>      0.4453</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2799,7 +3519,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.5058</x:v>
+        <x:v>      0.5107</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2814,7 +3534,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.6224</x:v>
+        <x:v>      0.6271</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2829,7 +3549,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.8001</x:v>
+        <x:v>      0.8014</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2859,7 +3579,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.6669</x:v>
+        <x:v>      1.6528</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2889,7 +3609,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.3521</x:v>
+        <x:v>      2.3132</x:v>
       </x:c>
     </x:row>
     <x:row>
